--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2018_coquimbo.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:46</t>
+    <t xml:space="preserve">2026-09-24 00:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -819,19 +819,19 @@
         <v>22</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.4</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>-0.27</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15">
@@ -842,19 +842,19 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>331</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-0.07</v>
       </c>
     </row>
     <row r="16">
@@ -865,19 +865,19 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>-0.26</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>-0.14</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>331</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>-0.17</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2018_coquimbo.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:37</t>
+    <t xml:space="preserve">2026-10-01 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2018_coquimbo.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:09</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
